--- a/output/full_scan/batch_seq5_2026-09-04.xlsx
+++ b/output/full_scan/batch_seq5_2026-09-04.xlsx
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.36869294358051</v>
+        <v>67.36869287322118</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.63485637254593</v>
+        <v>17.63485638438756</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0.9683224242501226</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3359396913900661</v>
+        <v>0.3359396913709803</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>971.7799327371772</v>
+        <v>971.7799327371806</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>32</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.84668499271884</v>
+        <v>56.84668521058833</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.02384575626702</v>
+        <v>20.02384585118786</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.952197527772653</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3820182269141308</v>
+        <v>0.382018226771034</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.94687262435185</v>
+        <v>65.94687261915863</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.4366682187659</v>
+        <v>31.43666821652394</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.238980830302148</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2840158483782737</v>
+        <v>0.2840158484068866</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.01323802924702</v>
+        <v>68.01323798331194</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.99456909886007</v>
+        <v>26.99456919285165</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0.9366503998766462</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2001522950741599</v>
+        <v>0.2001522951027813</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>843.2834102130138</v>
+        <v>843.283410213014</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>238</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.86867099534503</v>
+        <v>61.86867102598701</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.4626215720852</v>
+        <v>22.46262154883203</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.218183427622346</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.119811065633757</v>
+        <v>3.119811065061377</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>835.6517240612478</v>
+        <v>835.6517240612475</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>180</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.72068053833219</v>
+        <v>63.72068059341223</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14.67581622404458</v>
+        <v>14.67581625150088</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.429159641260894</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.799475399646696</v>
+        <v>1.799475399074323</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.25750226291944</v>
+        <v>61.25750240496395</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18.48392647572991</v>
+        <v>18.48392648550008</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>3.478773134818763</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1300377379541499</v>
+        <v>0.1300377377061196</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5475</v>
+        <v>4540</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>全球傳動</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>791.2890782949896</v>
+        <v>792.2081465766053</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>190</v>
+        <v>60.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.51633411985924</v>
+        <v>57.75629093549735</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.91796254236116</v>
+        <v>26.54672837067184</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6619925632042234</v>
+        <v>0.7298899817193959</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.579414058606023</v>
+        <v>0.0808433377585632</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6112</v>
+        <v>5475</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>785.8499413179406</v>
+        <v>791.2890782949896</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45.9</v>
+        <v>190</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>57.01009711488442</v>
+        <v>56.51633411985924</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.8825651362914</v>
+        <v>25.91796254236116</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.913270702857614</v>
+        <v>0.6619925632042234</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0059716690602321</v>
+        <v>2.579414058606023</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4540</v>
+        <v>6112</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>全球傳動</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>777.2081465766053</v>
+        <v>785.8499413179406</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>60.8</v>
+        <v>45.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.75629090256705</v>
+        <v>57.01009711488442</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.54672833451214</v>
+        <v>17.8825651362914</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7298899817193959</v>
+        <v>0.913270702857614</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>1</v>
@@ -1630,11 +1630,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.08084333784442151</v>
+        <v>0.0059716690602321</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>773.328183375708</v>
+        <v>783.328183375708</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>208.5</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.84613064913655</v>
+        <v>55.84613076113451</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.67274516073696</v>
+        <v>21.67274519599288</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.4680938240194797</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6018756494942719</v>
+        <v>0.6018756483495085</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5608</v>
+        <v>5443</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>四維航</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>771.5306889209247</v>
+        <v>771.2703314261742</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>17.2</v>
+        <v>112.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>60.28443753120546</v>
+        <v>59.9814724931512</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>37.428058488872</v>
+        <v>19.50330214895549</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5859662527690702</v>
+        <v>0.9576010316122472</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0220563407062523</v>
+        <v>0.7430224206304916</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5443</v>
+        <v>5471</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>松翰</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>771.2703314261742</v>
+        <v>768.2624933326335</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>112.5</v>
+        <v>61.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>59.9814724931512</v>
+        <v>58.99670378944448</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.50330214895549</v>
+        <v>12.02013384938513</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9576010316122472</v>
+        <v>0.4316616021818757</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>3</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.7430224206304916</v>
+        <v>0.3177876955653975</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5471</v>
+        <v>5608</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>松翰</t>
+          <t>四維航</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>768.2624933326335</v>
+        <v>761.5306889209247</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>61.1</v>
+        <v>17.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.99670378944448</v>
+        <v>60.28443750747787</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12.02013384938513</v>
+        <v>37.42805844136184</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4316616021818757</v>
+        <v>0.5859662527690702</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,11 +1842,11 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3177876955653975</v>
+        <v>-0.0220563406680945</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>37.35010562370299</v>
+        <v>37.3501056321872</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.70214483187329</v>
+        <v>27.70214485245994</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.347100668844813</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1056527962188895</v>
+        <v>0.1056527962284281</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>41.95682702329072</v>
+        <v>41.95682703261703</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.9080312854215</v>
+        <v>31.90803132596283</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.3283706515548287</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.633342375412959</v>
+        <v>-1.633342375508344</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4977</v>
+        <v>4770</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>上品</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>741.9698865168709</v>
+        <v>744.5367838518739</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>185</v>
+        <v>226.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.35411633510643</v>
+        <v>60.39884617721904</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.21019539032036</v>
+        <v>12.14893619565282</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.273288053299751</v>
+        <v>2.112234936040084</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.886043697421971</v>
+        <v>1.409762578793178</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4770</v>
+        <v>4977</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>上品</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>734.536783851874</v>
+        <v>741.9698865168709</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>226.5</v>
+        <v>185</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>60.398846013481</v>
+        <v>65.35411633510643</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>12.14893611107566</v>
+        <v>24.21019539032036</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.112234936040084</v>
+        <v>1.273288053299751</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,11 +2054,11 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.409762580128749</v>
+        <v>2.886043697421971</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.61396312690273</v>
+        <v>58.61396321237563</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>35.63466615009037</v>
+        <v>35.63466613631413</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.2794109483815408</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0514153649986103</v>
+        <v>-0.0514153650749311</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.07012543544468</v>
+        <v>58.07012551962736</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15.61035467798067</v>
+        <v>15.61035467491083</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.290810702760619</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1923439123285431</v>
+        <v>0.1923439122331468</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>655.8299076005721</v>
+        <v>645.8299076005718</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>330</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.25916324898145</v>
+        <v>54.25916326746803</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15.37248821028129</v>
+        <v>15.37248824231803</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>2.018898345037934</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.587082198429446</v>
+        <v>2.587082196998459</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.97837718985649</v>
+        <v>53.97837717034589</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>22.13982005732852</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.71965064179118</v>
+        <v>57.71965068149436</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>15.65147576081908</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1890550256326855</v>
+        <v>0.1890550255659024</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>57.7268946857125</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.64349662485681</v>
+        <v>23.64349666514575</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.8525328679749791</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.79676159235547</v>
+        <v>57.79677197860207</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.26789762105273</v>
+        <v>25.26790721588824</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.2324573232811756</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0125773918181401</v>
+        <v>0.0125773890611607</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>614.1711396732851</v>
+        <v>614.171139673285</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>17.4</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.76236789511151</v>
+        <v>59.76236785242209</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>32.438658877056</v>
+        <v>32.43865892371574</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.7894673174473317</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.155006167839906</v>
+        <v>0.1550061678589861</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.69805255771841</v>
+        <v>54.69805254089505</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.26872126466293</v>
+        <v>19.26872131606245</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.5399326075974193</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1593393394444415</v>
+        <v>0.1593393391582485</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.92674678556953</v>
+        <v>54.92674678482953</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.27131788845095</v>
+        <v>20.27131794083932</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>2.04331267434015</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>3.156074577081632</v>
+        <v>3.156074577043479</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>56.04603523311639</v>
+        <v>56.04603520415094</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>31.46395271335276</v>
+        <v>31.46395276095081</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.4208436309901667</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.09500715430617609</v>
+        <v>0.09500715417260799</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>545.5081171297853</v>
+        <v>545.5081171297852</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>32.75</v>
@@ -3788,7 +3788,7 @@
         <v>54.97908875094385</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.45712343882627</v>
+        <v>18.45712344100414</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.6457558226137</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3973250371389411</v>
+        <v>0.3973250371103249</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.26578454396629</v>
+        <v>50.26578465082562</v>
       </c>
       <c r="I66" s="2" t="n">
         <v>13.63541846608355</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0039819179455764</v>
+        <v>-0.0039819179665644</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>521.0325772997012</v>
+        <v>521.0325772997011</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>54.2</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.78058003848032</v>
+        <v>46.78057995967507</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26.49058737934373</v>
+        <v>26.49058727503832</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.4971249666247506</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.5866043037427814</v>
+        <v>-0.5866043040862097</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>62.44074237817028</v>
+        <v>62.44074239382279</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>35.67030135272804</v>
+        <v>35.67030132110823</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.495774442577636</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.34293221270564</v>
+        <v>-0.3429322127437988</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.1624142366178</v>
+        <v>47.16241423568868</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.58732113451458</v>
+        <v>12.58732113605856</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.7170628984006449</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>3.38645123861091</v>
+        <v>3.386451238477342</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.77839561051484</v>
+        <v>44.77839562282974</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.51415410580941</v>
+        <v>20.51415408317204</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.9907203777322376</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5408282129713933</v>
+        <v>0.5408282129618542</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>49.81238172050546</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10.46002081071876</v>
+        <v>10.46002083650135</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.6428797918041681</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.3937105895590911</v>
+        <v>-0.3937105896544439</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.77675493898979</v>
+        <v>49.7767549812358</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.3401689030022</v>
+        <v>11.34016875003766</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.359614990784354</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0015366813198366</v>
+        <v>0.0015366812435183</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>460.7218984610023</v>
+        <v>460.7218984610022</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>286.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.58006921583262</v>
+        <v>46.58006923525532</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.77010110062448</v>
+        <v>13.77010120025951</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.2846460996190745</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.244903062940855</v>
+        <v>1.244903062273014</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>4952</v>
+        <v>6125</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>449.933475257242</v>
+        <v>454.0808008003974</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.76822390490644</v>
+        <v>49.97666009235999</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.42550981567818</v>
+        <v>18.01389532545338</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3704228884001292</v>
+        <v>0.7019352333984005</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.032939518392515</v>
+        <v>0.1231901464266507</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>5460</v>
+        <v>4551</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>智伸科</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>445.3553838989167</v>
+        <v>450.6289679679033</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>16.25</v>
+        <v>171.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.4092535967955</v>
+        <v>52.11691091367082</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.34700528806667</v>
+        <v>12.81170095818818</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2416449629029787</v>
+        <v>1.494093026754936</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0057611513160374</v>
+        <v>1.980831581231631</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>5306</v>
+        <v>4952</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>桂盟</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>444.7600558577034</v>
+        <v>449.933475257242</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.37214851418986</v>
+        <v>48.76822390490644</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>26.60713269338178</v>
+        <v>12.42550981567818</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.336103991671301</v>
+        <v>0.3704228884001292</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.4526278282215588</v>
+        <v>-0.032939518392515</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>5439</v>
+        <v>5460</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>442.2021129150861</v>
+        <v>445.3553838989167</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>261.5</v>
+        <v>16.25</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.84488973999889</v>
+        <v>52.4092535967955</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.23471737405176</v>
+        <v>25.34700528806667</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5805943826987717</v>
+        <v>0.2416449629029787</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>3.880599918668359</v>
+        <v>0.0057611513160374</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>5347</v>
+        <v>5306</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>桂盟</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>441.245054674363</v>
+        <v>444.7600558577034</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>150</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.08206181386597</v>
+        <v>46.3721485891044</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7.806053925233409</v>
+        <v>26.6071326919606</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3349847931128435</v>
+        <v>1.336103991671301</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>2</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1580150414842975</v>
+        <v>-0.4526278287176413</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>5489</v>
+        <v>5439</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>437.8333412263287</v>
+        <v>442.2021129150861</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>41.4</v>
+        <v>261.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.68754318104019</v>
+        <v>53.84488973999889</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>19.31892063912918</v>
+        <v>20.23471737405176</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6781745541910408</v>
+        <v>0.5805943826987717</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.2566634680832911</v>
+        <v>3.880599918668359</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>5534</v>
+        <v>5347</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>長虹</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>437.5815752008942</v>
+        <v>441.245054674363</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>150</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,49 +5375,49 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.26757744130889</v>
+        <v>45.08206181386597</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.15890673538603</v>
+        <v>7.806053925233409</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4470359949471629</v>
+        <v>0.3349847931128435</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1459428042530287</v>
+        <v>0.1580150414842975</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>4583</v>
+        <v>5489</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>436.5581358597385</v>
+        <v>437.8333412263287</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>473.5</v>
+        <v>41.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.51724216151749</v>
+        <v>43.68754318104019</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>42.52543847328138</v>
+        <v>19.31892063912918</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.415520848500905</v>
+        <v>0.6781745541910408</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>1</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>3.691668805153441</v>
+        <v>0.2566634680832911</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4551</v>
+        <v>5534</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>智伸科</t>
+          <t>長虹</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>435.6289679679033</v>
+        <v>437.5815752008941</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>171.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>52.11691086793046</v>
+        <v>44.26757750945853</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.81170096626604</v>
+        <v>14.15890678310437</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.494093026754936</v>
+        <v>0.4470359949471629</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>1.980831581708605</v>
+        <v>-0.1459428045392241</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>4722</v>
+        <v>4583</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>國精化</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>432.1356576759364</v>
+        <v>436.5581358597385</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>200.5</v>
+        <v>473.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.07968435272434</v>
+        <v>43.51724218251513</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.10081071153147</v>
+        <v>42.52543847431097</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4812410546381001</v>
+        <v>0.415520848500905</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>1</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1428585150180046</v>
+        <v>3.691668804390275</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>4766</v>
+        <v>4722</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>國精化</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>430.1353495658734</v>
+        <v>432.1356576759364</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>346</v>
+        <v>200.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>54.82422649749121</v>
+        <v>44.07968439057957</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.76235803761692</v>
+        <v>12.10081071356431</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4640980907973914</v>
+        <v>0.4812410546381001</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>1</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.3428596232090291</v>
+        <v>0.1428585152087835</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>5522</v>
+        <v>4766</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>425.5230959232018</v>
+        <v>430.1353495658735</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>64</v>
+        <v>346</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.06191204068393</v>
+        <v>54.82422653793381</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.85581176739175</v>
+        <v>14.76235804798268</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5630102926036071</v>
+        <v>0.4640980907973914</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2081567914009544</v>
+        <v>0.3428596224458662</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6155</v>
+        <v>5522</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>424.8963482502063</v>
+        <v>425.5230959232018</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>56.2</v>
+        <v>64</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.17766724515305</v>
+        <v>50.06191203316749</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.97117444194076</v>
+        <v>12.8558118145084</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5203431964035549</v>
+        <v>0.5630102926036071</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2106391569817864</v>
+        <v>0.2081567914009544</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>4554</v>
+        <v>6155</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>424.2571036666508</v>
+        <v>424.8963482502063</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>29.3</v>
+        <v>56.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.35386945916827</v>
+        <v>46.17766724515305</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.71749088085744</v>
+        <v>11.97117444194076</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3056122787268613</v>
+        <v>0.5203431964035549</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.169391765588624</v>
+        <v>0.2106391569817864</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>5328</v>
+        <v>4554</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華容</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>423.7813658577199</v>
+        <v>424.2571036666508</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>61</v>
+        <v>29.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.5583442554108</v>
+        <v>41.35386945916827</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.513367017180649</v>
+        <v>17.71749088085744</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6082708178224383</v>
+        <v>0.3056122787268613</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.3841160361859943</v>
+        <v>-0.169391765588624</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>4542</v>
+        <v>5328</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>科嶠</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>420.2903707215624</v>
+        <v>423.7813658577199</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>283.5</v>
+        <v>61</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.47816708171651</v>
+        <v>46.5583442554108</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.68053399161092</v>
+        <v>9.513367017180649</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6009782605662775</v>
+        <v>0.6082708178224383</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>1</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>5.129428885863911</v>
+        <v>-0.3841160361859943</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>5488</v>
+        <v>4542</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>松普</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>419.4791273354944</v>
+        <v>420.2903707215624</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>12.1</v>
+        <v>283.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.76543535529491</v>
+        <v>49.47816708171651</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.38268403726326</v>
+        <v>14.68053399161092</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5225358378502525</v>
+        <v>0.6009782605662775</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>1</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0069341209584467</v>
+        <v>5.129428885863911</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6104</v>
+        <v>5488</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>松普</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>417.3562915541932</v>
+        <v>419.4791273354944</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>97</v>
+        <v>12.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.16227260055376</v>
+        <v>41.76543535529491</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.35624377067797</v>
+        <v>12.38268403726326</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.465721383670915</v>
+        <v>0.5225358378502525</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>1</v>
@@ -5976,51 +5976,51 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1732682778156746</v>
+        <v>0.0069341209584467</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>5371</v>
+        <v>6104</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>416.8780009303489</v>
+        <v>417.3562915541932</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>83.5</v>
+        <v>97</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G105" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.05997102322463</v>
+        <v>52.16227260055376</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.8483906684277</v>
+        <v>13.35624377067797</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.1790799411206339</v>
+        <v>0.465721383670915</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,51 +6029,51 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1002586937237013</v>
+        <v>0.1732682778156746</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>5245</v>
+        <v>5371</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>408.7824252315039</v>
+        <v>416.8780009303489</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>22.85</v>
+        <v>83.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G106" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>50.2215056872467</v>
+        <v>49.05997102322463</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>12.84959722830691</v>
+        <v>19.8483906684277</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.188387055966884</v>
+        <v>0.1790799411206339</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.275098498448664</v>
+        <v>-0.1002586937237013</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>4934</v>
+        <v>5245</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>404.6741854433132</v>
+        <v>408.7824252315039</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.9</v>
+        <v>22.85</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.83880642063016</v>
+        <v>50.2215056872467</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>23.26904774383351</v>
+        <v>12.84959722830691</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.053091684434968</v>
+        <v>1.188387055966884</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.018057525481967</v>
+        <v>0.275098498448664</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6160</v>
+        <v>4934</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>欣技</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>400.8970637260155</v>
+        <v>404.6741854433132</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14.75</v>
+        <v>13.9</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.41559209254063</v>
+        <v>41.83880642063016</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.49399643494204</v>
+        <v>23.26904774383351</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3789746399141729</v>
+        <v>1.053091684434968</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0248880968505298</v>
+        <v>0.018057525481967</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>4973</v>
+        <v>6160</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>欣技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>398.2429157424121</v>
+        <v>400.8970637260155</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>149.5</v>
+        <v>14.75</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.10205419580061</v>
+        <v>47.41559208148587</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.80461399618839</v>
+        <v>22.49399641257179</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4283658972660389</v>
+        <v>0.3789746399141729</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.7579153724088058</v>
+        <v>0.0248880968505298</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>4572</v>
+        <v>4973</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>駐龍</t>
+          <t>廣穎</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>397.7603314227056</v>
+        <v>398.2429157424121</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>141.5</v>
+        <v>149.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.55813627922352</v>
+        <v>47.10205419580061</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.48507102440568</v>
+        <v>10.80461399618839</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.1463783334679606</v>
+        <v>0.4283658972660389</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.3480381905190506</v>
+        <v>-0.7579153724088058</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>4755</v>
+        <v>4572</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>駐龍</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>395.9817304156413</v>
+        <v>397.7603314227057</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>118</v>
+        <v>141.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.07362016433339</v>
+        <v>49.55813626014653</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.85083840368774</v>
+        <v>18.4850710432554</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3981738875418733</v>
+        <v>0.1463783334679606</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.6111504208753396</v>
+        <v>0.3480381906144703</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>5309</v>
+        <v>4755</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>394.8923589317022</v>
+        <v>395.9817304156412</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,49 +6382,49 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.77072543180707</v>
+        <v>49.07362021360012</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.9948620806179</v>
+        <v>10.85083836146129</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5136267847993037</v>
+        <v>0.3981738875418733</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0537262073985247</v>
+        <v>0.6111504209707348</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>4440</v>
+        <v>5309</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>391.2522849689965</v>
+        <v>394.8923589317022</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>17.75</v>
+        <v>52</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,49 +6435,49 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>55.91544122293828</v>
+        <v>43.77072543180707</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>38.49109353936713</v>
+        <v>18.9948620806179</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5086696381451362</v>
+        <v>0.5136267847993037</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M113" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.005252598170192</v>
+        <v>0.0537262073985247</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>4195</v>
+        <v>4440</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>基米-創</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>389.4927042809678</v>
+        <v>391.2522849689965</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>13.75</v>
+        <v>17.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>29.15551127981657</v>
+        <v>55.91544114327672</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>23.05984881013723</v>
+        <v>38.49109360689381</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>2.366432473045128</v>
+        <v>0.5086696381451362</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0117137870533495</v>
+        <v>0.0052525981892716</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>5234</v>
+        <v>4195</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>基米-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>389.4108225757801</v>
+        <v>389.4927042809677</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>293</v>
+        <v>13.75</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,49 +6541,49 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>36.96796909620547</v>
+        <v>29.15551131845405</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>34.9270115065488</v>
+        <v>23.05984892937749</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.9993164979492768</v>
+        <v>2.366432473045128</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.48403130615986</v>
+        <v>0.0117137870533495</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6116</v>
+        <v>5234</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>388.6724574084339</v>
+        <v>389.4108225757801</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.05</v>
+        <v>293</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,49 +6594,49 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>47.59925314856063</v>
+        <v>36.96796909620547</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.72317254056752</v>
+        <v>34.9270115065488</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4637125705374429</v>
+        <v>0.9993164979492768</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0441995942408288</v>
+        <v>0.48403130615986</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>5269</v>
+        <v>6116</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>388.3001618422616</v>
+        <v>388.6724574084339</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>1430</v>
+        <v>14.05</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,49 +6647,49 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>50.11187674037271</v>
+        <v>47.59925314856063</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.85232992359619</v>
+        <v>20.72317254056752</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5867232929075246</v>
+        <v>0.4637125705374429</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>2.877871917462599</v>
+        <v>0.0441995942408288</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>4190</v>
+        <v>5269</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>佐登-KY</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>385.5892587102187</v>
+        <v>388.3001618422616</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25.95</v>
+        <v>1430</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,49 +6700,49 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>52.27776702494735</v>
+        <v>50.11187674037271</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.2999239084038</v>
+        <v>13.85232992359619</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6933064654107179</v>
+        <v>0.5867232929075246</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M118" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.447716166633754</v>
+        <v>2.877871917462599</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4999</v>
+        <v>4190</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>佐登-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>383.6078341772525</v>
+        <v>385.5892587102187</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>18.45</v>
+        <v>25.95</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.20198570582832</v>
+        <v>52.27776698568346</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.02385651014744</v>
+        <v>11.29992413074456</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5499799101114714</v>
+        <v>0.6933064654107179</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0165575284003654</v>
+        <v>0.4477161668627045</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>5498</v>
+        <v>4999</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>凱崴</t>
+          <t>鑫禾</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>383.1345403475102</v>
+        <v>383.6078341772525</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>53.4</v>
+        <v>18.45</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>51.41934629134886</v>
+        <v>40.20198570582832</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>21.5545711772202</v>
+        <v>13.02385651014744</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4155527638529956</v>
+        <v>0.5499799101114714</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.3279287072368138</v>
+        <v>-0.0165575284003654</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6121</v>
+        <v>5498</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>凱崴</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>381.8909380340733</v>
+        <v>383.1345403475102</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>397</v>
+        <v>53.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,49 +6859,49 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.42025860408197</v>
+        <v>51.41934629134886</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.85863083062612</v>
+        <v>21.5545711772202</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.36180637198139</v>
+        <v>0.4155527638529956</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.7085819289937811</v>
+        <v>0.3279287072368138</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4720</v>
+        <v>6121</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>德淵</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>381.6391672732855</v>
+        <v>381.8909380340733</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>18.6</v>
+        <v>397</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,49 +6912,49 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.27407191132124</v>
+        <v>49.42025860408197</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>20.6917288922188</v>
+        <v>14.85863083062612</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3569126372396931</v>
+        <v>0.36180637198139</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M122" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1668620518755846</v>
+        <v>-0.7085819289937811</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6118</v>
+        <v>4720</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>德淵</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>377.9397213738014</v>
+        <v>381.6391672732855</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>15.2</v>
+        <v>18.6</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.75082685766136</v>
+        <v>44.27407189937003</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.51203569943981</v>
+        <v>20.6917288922188</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2.373165942922403</v>
+        <v>0.3569126372396931</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0312672114747732</v>
+        <v>0.1668620518565043</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6103</v>
+        <v>6118</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>建達</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>376.1975776189981</v>
+        <v>377.9397213738014</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>37.2</v>
+        <v>15.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>53.83203283915083</v>
+        <v>40.75082685766136</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>11.48542898661993</v>
+        <v>13.51203569943981</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.9033031207137908</v>
+        <v>2.373165942922403</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>1.465975004606528</v>
+        <v>0.0312672114747732</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>5289</v>
+        <v>6103</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>375.3102912294883</v>
+        <v>376.1975776189981</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>1360</v>
+        <v>37.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>40.67982865692003</v>
+        <v>53.83203283915083</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.21012672455518</v>
+        <v>11.48542898661993</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6135597967424492</v>
+        <v>0.9033031207137908</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-16.73668429250288</v>
+        <v>1.465975004606528</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6139</v>
+        <v>5289</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>374.0965123993425</v>
+        <v>375.3102912294883</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>736</v>
+        <v>1360</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>43.11050594813348</v>
+        <v>40.67982865692003</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>17.0357366520417</v>
+        <v>12.21012672455518</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.9348174772424332</v>
+        <v>0.6135597967424492</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-4.747433650465265</v>
+        <v>-16.73668429250288</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>5493</v>
+        <v>6139</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>373.2184107759518</v>
+        <v>374.0965123993425</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>736</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>56.11702345828907</v>
+        <v>43.11050594813348</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>24.32622477254137</v>
+        <v>17.0357366520417</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6481030230165714</v>
+        <v>0.9348174772424332</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.7148529337398942</v>
+        <v>-4.747433650465265</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5481</v>
+        <v>5493</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>371.3756986376149</v>
+        <v>373.2184107759518</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>20.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>46.73204637625155</v>
+        <v>56.11702345828907</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>9.628381621766</v>
+        <v>24.32622477254137</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5197155292465443</v>
+        <v>0.6481030230165714</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,51 +7248,51 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.00339094357059</v>
+        <v>0.7148529337398942</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>6129</v>
+        <v>5481</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>普誠</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>370.5354129392288</v>
+        <v>371.3756986376149</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>13.1</v>
+        <v>20.2</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G129" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>31.60418960049736</v>
+        <v>46.73204637625155</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>28.6325462289654</v>
+        <v>9.628381621766</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.252905460925885</v>
+        <v>0.5197155292465443</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,51 +7301,51 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0150982656769856</v>
+        <v>0.00339094357059</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>5519</v>
+        <v>6129</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>普誠</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>369.8911613900282</v>
+        <v>370.5354129392288</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>27.35</v>
+        <v>13.1</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G130" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>32.25992053288154</v>
+        <v>31.60418965511853</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>30.93929996790195</v>
+        <v>28.63254627422414</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.9425880924698335</v>
+        <v>1.252905460925885</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0538237364811758</v>
+        <v>0.0150982656547327</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>6156</v>
+        <v>5519</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>松上</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>367.8131085926404</v>
+        <v>369.8911613900281</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>20.8</v>
+        <v>27.35</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>42.0133406599242</v>
+        <v>32.25992062410147</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>14.74121340269669</v>
+        <v>30.93929998173929</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.6942652338865837</v>
+        <v>0.9425880924698335</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>1</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.0808559245056399</v>
+        <v>0.0538237364334798</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>4169</v>
+        <v>6156</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>泰宗</t>
+          <t>松上</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>367.6044501015332</v>
+        <v>367.8131085926404</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>150.5</v>
+        <v>20.8</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>43.95742010076507</v>
+        <v>42.01334110792438</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>10.65724497020195</v>
+        <v>14.74121337529595</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.073211654007482</v>
+        <v>0.6942652338865837</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>1</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>1.459530533990836</v>
+        <v>0.0808559244388621</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>5465</v>
+        <v>4169</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>泰宗</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>365.6343013338092</v>
+        <v>367.6044501015332</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>24.3</v>
+        <v>150.5</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>56.03002283352592</v>
+        <v>43.95742009930153</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>25.27950104446554</v>
+        <v>10.65724499514098</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.8788287878681896</v>
+        <v>1.073211654007482</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>1</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0520185524161969</v>
+        <v>1.459530534028982</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>4552</v>
+        <v>5465</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>力達-KY</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>364.9597939576795</v>
+        <v>365.6343013338092</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>16.5</v>
+        <v>24.3</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>24.4477645175687</v>
+        <v>56.03002283352592</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>38.14842396466462</v>
+        <v>25.27950104446554</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.250099090251016</v>
+        <v>0.8788287878681896</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>1</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0179042631037705</v>
+        <v>0.0520185524161969</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>5386</v>
+        <v>4552</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>力達-KY</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>364.7011062804775</v>
+        <v>364.9597939576795</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>258.5</v>
+        <v>16.5</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46.66788096942</v>
+        <v>24.44776465537933</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>19.28484267129791</v>
+        <v>38.14842393658955</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.6450152503323531</v>
+        <v>2.250099090251016</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>7.077297159641272</v>
+        <v>-0.017904263151467</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>5871</v>
+        <v>5386</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>361.4918295472981</v>
+        <v>364.7011062804775</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>111.5</v>
+        <v>258.5</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,49 +7654,49 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45.29951149280124</v>
+        <v>46.66788096942</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.80070050681277</v>
+        <v>19.28484267129791</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.6792661614406247</v>
+        <v>0.6450152503323531</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.0497481117531264</v>
+        <v>7.077297159641272</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>5340</v>
+        <v>5871</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>360.8901417175596</v>
+        <v>361.4918295472984</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>79.2</v>
+        <v>111.5</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,49 +7707,49 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>51.08443266449017</v>
+        <v>45.29951152342305</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>19.76940447543847</v>
+        <v>12.80070051532098</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.4521566031754895</v>
+        <v>0.6792661614406247</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M137" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.2709138221280409</v>
+        <v>-0.0497481115623549</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5228</v>
+        <v>5340</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>358.2578855385318</v>
+        <v>360.8901417175596</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>41.7</v>
+        <v>79.2</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>47.70193404714369</v>
+        <v>51.08443266449017</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>17.38424385185864</v>
+        <v>19.76940447543847</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.060424704698584</v>
+        <v>0.4521566031754895</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>1</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.3001409875259826</v>
+        <v>0.2709138221280409</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>5223</v>
+        <v>5228</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>356.2917258635087</v>
+        <v>358.2578855385318</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>23.45</v>
+        <v>41.7</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>48.29805074433757</v>
+        <v>47.70193404714369</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>20.90710018919957</v>
+        <v>17.38424385185864</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.2755031657882636</v>
+        <v>1.060424704698584</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.0499300058469207</v>
+        <v>0.3001409875259826</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>5521</v>
+        <v>5223</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>工信</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>355.9990947050039</v>
+        <v>356.2917258635087</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>10.6</v>
+        <v>23.45</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>51.27012121173257</v>
+        <v>48.29805074433757</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>24.56114756874298</v>
+        <v>20.90710018919957</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.4663373847951508</v>
+        <v>0.2755031657882636</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.0347320371484056</v>
+        <v>0.0499300058469207</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>5225</v>
+        <v>5521</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>353.0635748332737</v>
+        <v>355.999094705004</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>57.4</v>
+        <v>10.6</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>27.85429224279485</v>
+        <v>51.27012121173257</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>25.34499310396287</v>
+        <v>24.56114759924036</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.668834975001673</v>
+        <v>0.4663373847951508</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.2020515948568388</v>
+        <v>-0.0347320371388642</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>4903</v>
+        <v>5225</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>346.6557386049797</v>
+        <v>353.0635748332737</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>36.95</v>
+        <v>57.4</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>49.66899746777344</v>
+        <v>27.85429224279485</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>10.98308160781715</v>
+        <v>25.34499310396287</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.9613203176398196</v>
+        <v>2.668834975001673</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.2413947605170867</v>
+        <v>0.2020515948568388</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>6124</v>
+        <v>4566</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>業強</t>
+          <t>時碩工業</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>344.8368534474544</v>
+        <v>346.8843024753443</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>27.15</v>
+        <v>63.9</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>51.83718322978224</v>
+        <v>41.53679880561335</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>11.73103916213401</v>
+        <v>12.11129722349423</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>1.613939109173128</v>
+        <v>0.216841106920507</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.4541270801588015</v>
+        <v>-0.708509364480864</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>5236</v>
+        <v>4903</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>343.398708687855</v>
+        <v>346.6557386049797</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>137.5</v>
+        <v>36.95</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>44.25829992612308</v>
+        <v>49.66899746777344</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>23.24597058560959</v>
+        <v>10.98308160781715</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>1.006049541809851</v>
+        <v>0.9613203176398196</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.680656550826491</v>
+        <v>0.2413947605170867</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>5345</v>
+        <v>6124</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>天揚</t>
+          <t>業強</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>341.3386052701538</v>
+        <v>344.8368534474544</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>21.9</v>
+        <v>27.15</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>47.24758009862817</v>
+        <v>51.83718332376261</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>6.237705111270726</v>
+        <v>11.7310391822273</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.1667582615839814</v>
+        <v>1.613939109173128</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.0624251370166002</v>
+        <v>0.4541270798249111</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>4958</v>
+        <v>5236</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>339.4303993624227</v>
+        <v>343.398708687855</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>463</v>
+        <v>137.5</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,16 +8184,16 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>46.53119440337254</v>
+        <v>44.25829992612308</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>13.32173687349067</v>
+        <v>23.24597058560959</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.9442757384834504</v>
+        <v>1.006049541809851</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>3.640374039453174</v>
+        <v>0.680656550826491</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>4729</v>
+        <v>5345</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>天揚</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>339.3156947264676</v>
+        <v>341.3386052701538</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>19</v>
+        <v>21.9</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>45.44160571259641</v>
+        <v>47.24758009862817</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>18.4104433980595</v>
+        <v>6.237705111270726</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.4145861149534748</v>
+        <v>0.1667582615839814</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0501091399698307</v>
+        <v>0.0624251370166002</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>6125</v>
+        <v>4958</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>339.0808008003971</v>
+        <v>339.4303993624227</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>51.5</v>
+        <v>463</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,13 +8290,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>49.97665988159251</v>
+        <v>46.53119440337254</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>18.01389531693314</v>
+        <v>13.32173687349067</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.7019352333984005</v>
+        <v>0.9442757384834504</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.1231901465602049</v>
+        <v>3.640374039453174</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>6123</v>
+        <v>4729</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>335.7074969165697</v>
+        <v>339.3156947264676</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>43.6</v>
+        <v>19</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>58.54009938745554</v>
+        <v>45.44160571259641</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>6.812839991637818</v>
+        <v>18.4104433980595</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.6309665831132796</v>
+        <v>0.4145861149534748</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>0</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.0292960977445608</v>
+        <v>0.0501091399698307</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>5287</v>
+        <v>6123</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>333.0668130039812</v>
+        <v>335.7074969165697</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>135.5</v>
+        <v>43.6</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,49 +8396,49 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>25.97310807626121</v>
+        <v>58.54009938745554</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>40.13490313206396</v>
+        <v>6.812839991637818</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.5066813003981168</v>
+        <v>0.6309665831132796</v>
       </c>
       <c r="K150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-1.900430440561666</v>
+        <v>0.0292960977445608</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, invest_trust_buy_2d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>4566</v>
+        <v>5287</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>時碩工業</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>331.8843024753443</v>
+        <v>333.0668130039812</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>63.9</v>
+        <v>135.5</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,29 +8449,29 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>41.53679877368996</v>
+        <v>25.97310807626121</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>12.11129720684783</v>
+        <v>40.13490313206396</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.216841106920507</v>
+        <v>0.5066813003981168</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M151" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.7085093644045468</v>
+        <v>-1.900430440561666</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>327.6222467321139</v>
+        <v>327.622246732111</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>60.6</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>51.76419299426842</v>
+        <v>51.76419298404657</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>12.26574772243894</v>
+        <v>12.26574773619308</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.003083246462432</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.0419385634994242</v>
+        <v>0.0419385635566579</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>51.1497772646098</v>
+        <v>51.14977730409412</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>11.9457609207915</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.2059754295106612</v>
+        <v>-0.2059754298922667</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>48.83164028774858</v>
+        <v>48.83164046553718</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>16.77797871017355</v>
+        <v>16.77797871868222</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.9561139975008758</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.0030702118466017</v>
+        <v>0.0030702118084434</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -9007,21 +9007,21 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>4746</v>
+        <v>6146</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>耕興</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>307.3305451155052</v>
+        <v>305.1137285022982</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>45.35</v>
+        <v>182.5</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,13 +9032,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>27.30684711595221</v>
+        <v>34.04488645376215</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>20.37765847898006</v>
+        <v>10.5741395604197</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1.133054511550517</v>
+        <v>2.13167265452114</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>0</v>
@@ -9050,31 +9050,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.6120932819622426</v>
+        <v>-0.8835136536233759</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>6146</v>
+        <v>5490</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>耕興</t>
+          <t>同亨</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>305.1137285022982</v>
+        <v>304.7938605502576</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>182.5</v>
+        <v>26.5</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>34.04488646116467</v>
+        <v>31.93443200236891</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>10.57413949105714</v>
+        <v>17.62305062921899</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>2.13167265452114</v>
+        <v>0.7689537672889889</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.8835136536233759</v>
+        <v>-0.3141202899824519</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>5490</v>
+        <v>4951</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>同亨</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>304.7938605502576</v>
+        <v>303.58006218631</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>26.5</v>
+        <v>80</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,16 +9138,16 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>31.93443200236891</v>
+        <v>50.62679051255924</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>17.62305062921899</v>
+        <v>18.52471568600406</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.7689537672889889</v>
+        <v>0.920427037721876</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.3141202899824519</v>
+        <v>0.6373891135355758</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>4951</v>
+        <v>4441</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>振大環球</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>303.58006218631</v>
+        <v>300.4046246022454</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>50.62679051255924</v>
+        <v>41.91808947580145</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>18.52471568600406</v>
+        <v>21.94739276321648</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.920427037721876</v>
+        <v>0.6287921653363112</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>1</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0.6373891135355758</v>
+        <v>-1.36872330379065</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>4441</v>
+        <v>5484</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>振大環球</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>300.4046246022454</v>
+        <v>299.8082922189407</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>175</v>
+        <v>39.5</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>41.9180893821086</v>
+        <v>43.47227853289363</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>21.94739269214829</v>
+        <v>9.160549590208641</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.6287921653363112</v>
+        <v>0.4563113811461133</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>1</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-1.368723305316996</v>
+        <v>0.0277613936608263</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>5484</v>
+        <v>5381</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>299.8082922189407</v>
+        <v>299.0677007184117</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>39.5</v>
+        <v>24.65</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>43.47227853289363</v>
+        <v>46.64165951151938</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>9.160549590208641</v>
+        <v>18.17720801552344</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.4563113811461133</v>
+        <v>0.6998109452763971</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.0277613936608263</v>
+        <v>0.0859993542419477</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>5381</v>
+        <v>5203</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>299.0677007184117</v>
+        <v>297.8847258709467</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>24.65</v>
+        <v>58.8</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>46.64165951151938</v>
+        <v>36.08056001891667</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>18.17720801552344</v>
+        <v>30.41801368410305</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.6998109452763971</v>
+        <v>0.6424922494914914</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
@@ -9368,31 +9368,31 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.0859993542419477</v>
+        <v>0.1752303382113709</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>5203</v>
+        <v>5215</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>297.8847258709467</v>
+        <v>297.6533541989182</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>58.8</v>
+        <v>38.95</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,16 +9403,16 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>36.08056001891667</v>
+        <v>44.94370458269636</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>30.41801368410305</v>
+        <v>11.95057016385661</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.6424922494914914</v>
+        <v>0.3780480472742577</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>0</v>
@@ -9421,31 +9421,31 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.1752303382113709</v>
+        <v>-0.0058717430978437</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>5215</v>
+        <v>4916</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>297.6533541989182</v>
+        <v>296.6374010412167</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>38.95</v>
+        <v>97.3</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,16 +9456,16 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>44.94370458269636</v>
+        <v>42.9490003749787</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>11.95057016385661</v>
+        <v>8.118049394753369</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.3780480472742577</v>
+        <v>0.3064053978890404</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.0058717430978437</v>
+        <v>-0.3865892889267904</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>4916</v>
+        <v>4942</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>296.6374010412167</v>
+        <v>296.3063599946648</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>97.3</v>
+        <v>33.1</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,16 +9509,16 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>42.9490003749787</v>
+        <v>34.69331760779575</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>8.118049394753369</v>
+        <v>42.25733170203522</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.3064053978890404</v>
+        <v>0.355808831842746</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.3865892889267904</v>
+        <v>0.1021575574313931</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>4942</v>
+        <v>4536</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>拓凱</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>296.3063599946648</v>
+        <v>293.8083092624495</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>33.1</v>
+        <v>164.5</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,13 +9562,13 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>34.69331760779575</v>
+        <v>43.29210976208933</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>42.25733170203522</v>
+        <v>16.76544486143494</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.355808831842746</v>
+        <v>0.5892055683286802</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.1021575574313931</v>
+        <v>-0.7243431646337961</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>4536</v>
+        <v>4746</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>拓凱</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>293.8083092624495</v>
+        <v>292.3305451155052</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>164.5</v>
+        <v>45.35</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>43.29210958531115</v>
+        <v>27.30684711595221</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>16.76544486519134</v>
+        <v>20.37765849825889</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.5892055683286802</v>
+        <v>1.133054511550517</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>0</v>
@@ -9633,11 +9633,11 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.7243431638706207</v>
+        <v>-0.6120932820194853</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>47.16430328405337</v>
+        <v>47.16430326333838</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>10.47949719034352</v>
+        <v>10.47949720992704</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.4637169299192256</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.0259495490899889</v>
+        <v>0.0259495490709118</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>41.41332567589042</v>
+        <v>41.41332582350904</v>
       </c>
       <c r="I177" s="2" t="n">
         <v>11.91950037333316</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.0940535494125794</v>
+        <v>-0.0940535496796914</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>273.9837566488512</v>
+        <v>273.9837566488516</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>46.25</v>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>48.92304786465698</v>
+        <v>48.9230478841434</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>15.32216338842216</v>
+        <v>15.32216333663878</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.5152017379864441</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.1557793311009305</v>
+        <v>-0.1557793311486358</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>39.40142753844782</v>
+        <v>39.40142708572234</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>15.34432077417234</v>
+        <v>15.34432103184308</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>1.094969175781118</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.0252955283873512</v>
+        <v>0.02529552863538</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>44.32996117622391</v>
+        <v>44.329961191834</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>13.34472378641721</v>
+        <v>13.3447237994732</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.3957798044657901</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.106790668907565</v>
+        <v>0.1067906687358468</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>36.94640166338987</v>
+        <v>36.94640169232822</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>29.37440682054528</v>
+        <v>29.37440686685824</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.639964688293837</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.09717359878965599</v>
+        <v>0.09717359875149641</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>244.6839769853053</v>
+        <v>244.6839769853052</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>28.9</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>27.46428687200052</v>
+        <v>27.46428682953454</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>21.67991153796517</v>
+        <v>21.67991149959801</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.8291373195802236</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.3369255994694878</v>
+        <v>-0.3369255994981082</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>39.5958743002378</v>
+        <v>39.59587456955608</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>14.79194721250754</v>
+        <v>14.79194718161222</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.859490652288621</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0022349524862961</v>
+        <v>-0.0022349527724987</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>37.9029661857575</v>
+        <v>37.90296623933886</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>10.44432171423793</v>
+        <v>10.44432175972087</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.3714149206307749</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.2316849176276336</v>
+        <v>-0.2316849178184279</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>236.4068659429498</v>
+        <v>236.4068659429499</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>16.9</v>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>41.89100577067558</v>
+        <v>41.89100587852823</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>12.43845794163714</v>
+        <v>12.43845800068179</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.6350739686215084</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.037691566332205</v>
+        <v>-0.0376915663512844</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>44.16084252369999</v>
+        <v>44.16084254846221</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>10.67185605183598</v>
+        <v>10.67185605811116</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.7579798373516736</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.0268902524675247</v>
+        <v>0.0268902524293652</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>44.40889021270083</v>
+        <v>44.40889022644154</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>15.67724240431055</v>
+        <v>15.67724242639393</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>1.148387903826559</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.0524986419738011</v>
+        <v>-0.0524986420119572</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>42.51362327180379</v>
+        <v>42.5136232932622</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>17.41273941367714</v>
+        <v>17.4127394267289</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.4860354515693703</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.0385597949966225</v>
+        <v>-0.0385597949775481</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>42.85933560464778</v>
+        <v>42.85933567287573</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>16.28578466620536</v>
+        <v>16.28578472063752</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.3700900109769484</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.5874274312855212</v>
+        <v>-0.5874274316098788</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>46.35140671632444</v>
+        <v>46.35140666048677</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>18.08416362729971</v>
+        <v>18.08416363750749</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.4294407148425229</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.2604865652945616</v>
+        <v>-0.2604865654853549</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>33.17333683351144</v>
+        <v>33.173337020513</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>11.83331807302089</v>
+        <v>11.83331803836223</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.6327650175120193</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>-0.0132910803027249</v>
+        <v>-0.0132910803218055</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>52.42157969309176</v>
+        <v>52.4215797791633</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>13.90809710425775</v>
+        <v>13.90809721168094</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>0.5186539063974922</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>-0.0050776973377037</v>
+        <v>-0.0050776974330989</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>44.39153432762285</v>
+        <v>44.39153444500467</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>6.509798961813392</v>
+        <v>6.509799207305508</v>
       </c>
       <c r="J231" s="2" t="n">
         <v>0.4403308631345899</v>
@@ -12707,7 +12707,7 @@
         <v>-1</v>
       </c>
       <c r="N231" s="2" t="n">
-        <v>-1.196738515345216</v>
+        <v>-1.196738524884944</v>
       </c>
       <c r="O231" s="2" t="inlineStr">
         <is>
@@ -12795,10 +12795,10 @@
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>43.14591549327917</v>
+        <v>43.14591539203859</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>17.3349976532041</v>
+        <v>17.33499768634242</v>
       </c>
       <c r="J233" s="2" t="n">
         <v>0.8988457271039164</v>
@@ -12813,7 +12813,7 @@
         <v>-1</v>
       </c>
       <c r="N233" s="2" t="n">
-        <v>0.0100457109914245</v>
+        <v>0.0100457110105037</v>
       </c>
       <c r="O233" s="2" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>51.24774133088582</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>15.81363140623483</v>
+        <v>15.8136315288875</v>
       </c>
       <c r="J235" s="2" t="n">
         <v>0.3677988499589271</v>
